--- a/interview_forms/008_sales_candidate_pre_screening--interview_forms.xlsx
+++ b/interview_forms/008_sales_candidate_pre_screening--interview_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -765,8 +765,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="31" customWidth="1" min="2" max="2"/>
+    <col width="31" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -794,12 +794,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'name':_'phone',_'label':_'phone'}</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'name': 'Phone', 'label': 'Phone'}</t>
+          <t>Phone</t>
         </is>
       </c>
     </row>
@@ -811,12 +811,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'name':_'email',_'label':_'email'}</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'name': 'Email', 'label': 'Email'}</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
@@ -828,12 +828,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'name':_'address',_'label':_'address'}</t>
+          <t>address</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'name': 'Address', 'label': 'Address'}</t>
+          <t>Address</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'name':_1,_'label':_0}</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'name': 1, 'label': 0}</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -862,12 +862,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'name':_2,_'label':_'1-5_years'}</t>
+          <t>1-5_years</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'name': 2, 'label': '1-5 years'}</t>
+          <t>1-5 years</t>
         </is>
       </c>
     </row>
@@ -879,12 +879,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'name':_3,_'label':_'5-10_years'}</t>
+          <t>5-10_years</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'name': 3, 'label': '5-10 years'}</t>
+          <t>5-10 years</t>
         </is>
       </c>
     </row>
@@ -896,12 +896,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'name':_4,_'label':_'more_than_10_years'}</t>
+          <t>more_than_10_years</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'name': 4, 'label': 'More than 10 years'}</t>
+          <t>More than 10 years</t>
         </is>
       </c>
     </row>
@@ -913,12 +913,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'name':_1,_'label':_'sales_candidate_pre_screening'}</t>
+          <t>sales_candidate_pre_screening</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'name': 1, 'label': 'Sales Candidate Pre Screening'}</t>
+          <t>Sales Candidate Pre Screening</t>
         </is>
       </c>
     </row>
@@ -930,12 +930,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'name':_2,_'label':_'sales_lead_form'}</t>
+          <t>sales_lead_form</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'name': 2, 'label': 'Sales Lead Form'}</t>
+          <t>Sales Lead Form</t>
         </is>
       </c>
     </row>
@@ -947,12 +947,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'name':_3,_'label':_'other_form'}</t>
+          <t>other_form</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'name': 3, 'label': 'Other Form'}</t>
+          <t>Other Form</t>
         </is>
       </c>
     </row>
